--- a/catalog_produse_pv.xlsx
+++ b/catalog_produse_pv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tehni\Desktop\Gabi\CLAUDE oferta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAABFD3A-B5ED-44DD-8900-5CAEDB33A756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DCD925-B49E-4B45-9F79-A9DB99BDBA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucțiuni" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="167">
   <si>
     <t>CATALOG PRODUSE PV — Ghid de utilizare</t>
   </si>
@@ -289,9 +289,6 @@
   </si>
   <si>
     <t>Invertor trifazat Goodwe GW25KN-ET HV 25kW (HV)</t>
-  </si>
-  <si>
-    <t>EUR</t>
   </si>
   <si>
     <t>Solis</t>
@@ -775,7 +772,19 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -793,22 +802,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1084,18 +1081,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
     </row>
     <row r="3" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -1129,7 +1126,7 @@
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1141,11 +1138,11 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
@@ -1212,11 +1209,11 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
     </row>
     <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
@@ -1275,11 +1272,11 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="24" t="s">
+      <c r="A29" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="24"/>
-      <c r="C29" s="24"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
     </row>
     <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
@@ -1397,16 +1394,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -1696,10 +1693,10 @@
     </row>
     <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>71</v>
@@ -1722,10 +1719,10 @@
     </row>
     <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>71</v>
@@ -1748,10 +1745,10 @@
     </row>
     <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>71</v>
@@ -1774,10 +1771,10 @@
     </row>
     <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>71</v>
@@ -1800,10 +1797,10 @@
     </row>
     <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>71</v>
@@ -1826,10 +1823,10 @@
     </row>
     <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>71</v>
@@ -1852,10 +1849,10 @@
     </row>
     <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>71</v>
@@ -1878,10 +1875,10 @@
     </row>
     <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>71</v>
@@ -1892,10 +1889,10 @@
       <c r="E20" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="19">
         <v>12</v>
       </c>
-      <c r="G20" s="27">
+      <c r="G20" s="20">
         <v>6858</v>
       </c>
       <c r="H20" s="4" t="s">
@@ -1904,10 +1901,10 @@
     </row>
     <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>71</v>
@@ -1918,10 +1915,10 @@
       <c r="E21" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="19">
         <v>14</v>
       </c>
-      <c r="G21" s="27">
+      <c r="G21" s="20">
         <v>7297</v>
       </c>
       <c r="H21" s="4" t="s">
@@ -1930,10 +1927,10 @@
     </row>
     <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>71</v>
@@ -1944,10 +1941,10 @@
       <c r="E22" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="19">
         <v>16</v>
       </c>
-      <c r="G22" s="27">
+      <c r="G22" s="20">
         <v>8190</v>
       </c>
       <c r="H22" s="4" t="s">
@@ -1956,10 +1953,10 @@
     </row>
     <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>71</v>
@@ -1970,10 +1967,10 @@
       <c r="E23" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F23" s="26">
+      <c r="F23" s="19">
         <v>18</v>
       </c>
-      <c r="G23" s="27">
+      <c r="G23" s="20">
         <v>8019</v>
       </c>
       <c r="H23" s="4" t="s">
@@ -1982,10 +1979,10 @@
     </row>
     <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>86</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>87</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>79</v>
@@ -2008,10 +2005,10 @@
     </row>
     <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>79</v>
@@ -2034,10 +2031,10 @@
     </row>
     <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>79</v>
@@ -2060,10 +2057,10 @@
     </row>
     <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>79</v>
@@ -2086,10 +2083,10 @@
     </row>
     <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="28" t="s">
-        <v>154</v>
+        <v>85</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>153</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>79</v>
@@ -2100,10 +2097,10 @@
       <c r="E28" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F28" s="26">
+      <c r="F28" s="19">
         <v>5</v>
       </c>
-      <c r="G28" s="27">
+      <c r="G28" s="20">
         <v>4903</v>
       </c>
       <c r="H28" s="4" t="s">
@@ -2112,10 +2109,10 @@
     </row>
     <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B29" s="28" t="s">
-        <v>155</v>
+        <v>85</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>154</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>79</v>
@@ -2126,10 +2123,10 @@
       <c r="E29" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="22">
         <v>6</v>
       </c>
-      <c r="G29" s="30">
+      <c r="G29" s="23">
         <v>4590</v>
       </c>
       <c r="H29" s="4" t="s">
@@ -2138,10 +2135,10 @@
     </row>
     <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B30" s="28" t="s">
-        <v>156</v>
+        <v>85</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>155</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>79</v>
@@ -2152,10 +2149,10 @@
       <c r="E30" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="26">
+      <c r="F30" s="19">
         <v>8</v>
       </c>
-      <c r="G30" s="27">
+      <c r="G30" s="20">
         <v>4841</v>
       </c>
       <c r="H30" s="4" t="s">
@@ -2164,10 +2161,10 @@
     </row>
     <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B31" s="28" t="s">
-        <v>157</v>
+        <v>85</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>79</v>
@@ -2178,10 +2175,10 @@
       <c r="E31" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="29">
+      <c r="F31" s="22">
         <v>10</v>
       </c>
-      <c r="G31" s="30">
+      <c r="G31" s="23">
         <v>5144</v>
       </c>
       <c r="H31" s="4" t="s">
@@ -2190,10 +2187,10 @@
     </row>
     <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>79</v>
@@ -2216,10 +2213,10 @@
     </row>
     <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>79</v>
@@ -2242,10 +2239,10 @@
     </row>
     <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>79</v>
@@ -2268,10 +2265,10 @@
     </row>
     <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>79</v>
@@ -2294,10 +2291,10 @@
     </row>
     <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>79</v>
@@ -2320,10 +2317,10 @@
     </row>
     <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>79</v>
@@ -2346,10 +2343,10 @@
     </row>
     <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>79</v>
@@ -2812,15 +2809,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
+      <c r="A1" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="2" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -2830,13 +2827,13 @@
         <v>62</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>93</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>94</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>67</v>
@@ -2850,7 +2847,7 @@
         <v>69</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>72</v>
@@ -2873,7 +2870,7 @@
         <v>69</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>72</v>
@@ -2896,7 +2893,7 @@
         <v>69</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>72</v>
@@ -2919,7 +2916,7 @@
         <v>69</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>77</v>
@@ -2939,10 +2936,10 @@
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>99</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>100</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>72</v>
@@ -2951,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F7" s="17">
         <v>3262.23</v>
@@ -2962,10 +2959,10 @@
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>72</v>
@@ -2974,7 +2971,7 @@
         <v>5</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F8" s="11">
         <v>8200</v>
@@ -2985,10 +2982,10 @@
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>72</v>
@@ -3003,15 +3000,15 @@
         <v>3267</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>72</v>
@@ -3026,15 +3023,15 @@
         <v>6769</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>77</v>
@@ -3049,15 +3046,15 @@
         <v>3492</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="B12" s="14" t="s">
         <v>165</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>166</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>72</v>
@@ -3195,15 +3192,15 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" t="s">
         <v>106</v>
-      </c>
-      <c r="B2" t="s">
-        <v>107</v>
       </c>
       <c r="C2" t="s">
         <v>25</v>
@@ -3211,7 +3208,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B3">
         <v>460</v>
@@ -3222,7 +3219,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B4">
         <v>490</v>
@@ -3233,7 +3230,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B5">
         <v>625</v>
@@ -3258,166 +3255,166 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" t="s">
         <v>111</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>112</v>
-      </c>
-      <c r="C1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B3">
         <v>5000</v>
       </c>
       <c r="C3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B4">
         <v>8430</v>
       </c>
       <c r="C4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B5">
         <v>15190</v>
       </c>
       <c r="C5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B6">
         <v>500</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B7">
         <v>1600</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B8">
         <v>2500</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B9">
         <v>2000</v>
       </c>
       <c r="C9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B10">
         <v>3500</v>
       </c>
       <c r="C10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B12">
         <v>190</v>
       </c>
       <c r="C12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B13">
         <v>170</v>
       </c>
       <c r="C13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B14">
         <v>220</v>
       </c>
       <c r="C14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B15">
         <v>250</v>
       </c>
       <c r="C15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B16">
         <v>350</v>
       </c>
       <c r="C16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/catalog_produse_pv.xlsx
+++ b/catalog_produse_pv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tehni\Desktop\Gabi\CLAUDE oferta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DCD925-B49E-4B45-9F79-A9DB99BDBA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078C3617-FD0D-41A1-859C-860B92A8842D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1155" yWindow="3525" windowWidth="15375" windowHeight="11580" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucțiuni" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="168">
   <si>
     <t>CATALOG PRODUSE PV — Ghid de utilizare</t>
   </si>
@@ -456,12 +456,6 @@
     <t>Sol (structura fixa) - RON per panou montat</t>
   </si>
   <si>
-    <t>struct_carport_per_panou</t>
-  </si>
-  <si>
-    <t>Carport/Pergola - RON per panou montat</t>
-  </si>
-  <si>
     <t>Oferta actualizata 20.05.2026</t>
   </si>
   <si>
@@ -538,6 +532,15 @@
   </si>
   <si>
     <t>DYNESS DL5.0C-heat wifi 5,12</t>
+  </si>
+  <si>
+    <t>struct_sandwich_per_panou</t>
+  </si>
+  <si>
+    <t>Minirail/sandwich - RON per panou montat</t>
+  </si>
+  <si>
+    <t>AstroEnergy</t>
   </si>
 </sst>
 </file>
@@ -787,6 +790,9 @@
     <xf numFmtId="4" fontId="9" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -801,9 +807,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1081,18 +1084,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
     </row>
     <row r="3" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -1126,7 +1129,7 @@
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1138,11 +1141,11 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
@@ -1209,11 +1212,11 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
     </row>
     <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
@@ -1272,11 +1275,11 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
     </row>
     <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
@@ -1394,16 +1397,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -1696,7 +1699,7 @@
         <v>85</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>71</v>
@@ -1722,7 +1725,7 @@
         <v>85</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>71</v>
@@ -1748,7 +1751,7 @@
         <v>85</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>71</v>
@@ -1774,7 +1777,7 @@
         <v>85</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>71</v>
@@ -1800,7 +1803,7 @@
         <v>85</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>71</v>
@@ -1826,7 +1829,7 @@
         <v>85</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>71</v>
@@ -1852,7 +1855,7 @@
         <v>85</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>71</v>
@@ -1878,7 +1881,7 @@
         <v>85</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>71</v>
@@ -1904,7 +1907,7 @@
         <v>85</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>71</v>
@@ -1930,7 +1933,7 @@
         <v>85</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>71</v>
@@ -1956,7 +1959,7 @@
         <v>85</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>71</v>
@@ -2086,7 +2089,7 @@
         <v>85</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>79</v>
@@ -2112,7 +2115,7 @@
         <v>85</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>79</v>
@@ -2138,7 +2141,7 @@
         <v>85</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>79</v>
@@ -2164,7 +2167,7 @@
         <v>85</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>79</v>
@@ -2190,7 +2193,7 @@
         <v>85</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>79</v>
@@ -2216,7 +2219,7 @@
         <v>85</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>79</v>
@@ -2242,7 +2245,7 @@
         <v>85</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>79</v>
@@ -2268,7 +2271,7 @@
         <v>85</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>79</v>
@@ -2294,7 +2297,7 @@
         <v>85</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>79</v>
@@ -2320,7 +2323,7 @@
         <v>85</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>79</v>
@@ -2346,7 +2349,7 @@
         <v>85</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>79</v>
@@ -2368,7 +2371,9 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="8"/>
+      <c r="A39" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="B39" s="9"/>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
@@ -2378,7 +2383,9 @@
       <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="4"/>
+      <c r="A40" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="B40" s="5"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -2388,7 +2395,9 @@
       <c r="H40" s="8"/>
     </row>
     <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="8"/>
+      <c r="A41" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="B41" s="9"/>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
@@ -2398,7 +2407,9 @@
       <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="4"/>
+      <c r="A42" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="B42" s="5"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -2408,7 +2419,9 @@
       <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="8"/>
+      <c r="A43" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="B43" s="9"/>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
@@ -2418,7 +2431,9 @@
       <c r="H43" s="8"/>
     </row>
     <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="8"/>
+      <c r="A44" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="B44" s="9"/>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
@@ -2428,7 +2443,9 @@
       <c r="H44" s="8"/>
     </row>
     <row r="45" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="4"/>
+      <c r="A45" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="B45" s="5"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
@@ -2438,7 +2455,9 @@
       <c r="H45" s="4"/>
     </row>
     <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="8"/>
+      <c r="A46" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="B46" s="9"/>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
@@ -2448,7 +2467,9 @@
       <c r="H46" s="8"/>
     </row>
     <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="4"/>
+      <c r="A47" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="B47" s="5"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
@@ -2458,7 +2479,9 @@
       <c r="H47" s="4"/>
     </row>
     <row r="48" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="8"/>
+      <c r="A48" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="B48" s="9"/>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
@@ -2468,7 +2491,9 @@
       <c r="H48" s="8"/>
     </row>
     <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="4"/>
+      <c r="A49" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="B49" s="5"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
@@ -2478,7 +2503,9 @@
       <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="8"/>
+      <c r="A50" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="B50" s="9"/>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
@@ -2488,7 +2515,9 @@
       <c r="H50" s="8"/>
     </row>
     <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="4"/>
+      <c r="A51" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="B51" s="5"/>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
@@ -2982,10 +3011,10 @@
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>164</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>166</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>72</v>
@@ -3005,7 +3034,7 @@
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>102</v>
@@ -3028,7 +3057,7 @@
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>103</v>
@@ -3051,10 +3080,10 @@
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>72</v>
@@ -3183,7 +3212,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F213540-DFB1-4AE5-8B23-D983343261EE}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="14.140625" customWidth="1"/>
@@ -3237,6 +3266,17 @@
       </c>
       <c r="C5">
         <v>420</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6">
+        <v>460</v>
+      </c>
+      <c r="C6">
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -3367,7 +3407,7 @@
         <v>131</v>
       </c>
       <c r="B12">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="C12" t="s">
         <v>132</v>
@@ -3389,7 +3429,7 @@
         <v>135</v>
       </c>
       <c r="B14">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="C14" t="s">
         <v>136</v>
@@ -3400,7 +3440,7 @@
         <v>137</v>
       </c>
       <c r="B15">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="C15" t="s">
         <v>138</v>
@@ -3408,13 +3448,13 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="B16">
-        <v>350</v>
+        <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>

--- a/catalog_produse_pv.xlsx
+++ b/catalog_produse_pv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tehni\Desktop\Gabi\CLAUDE oferta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078C3617-FD0D-41A1-859C-860B92A8842D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555D2A44-01E8-4302-840C-905FCE8AE792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1155" yWindow="3525" windowWidth="15375" windowHeight="11580" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14100" yWindow="2670" windowWidth="15375" windowHeight="11580" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucțiuni" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="166">
   <si>
     <t>CATALOG PRODUSE PV — Ghid de utilizare</t>
   </si>
@@ -360,15 +360,6 @@
     <t>Putere Wp</t>
   </si>
   <si>
-    <t>Jinko 460</t>
-  </si>
-  <si>
-    <t>Jinko 490</t>
-  </si>
-  <si>
-    <t>Jinko 625</t>
-  </si>
-  <si>
     <t>Cheie</t>
   </si>
   <si>
@@ -541,6 +532,9 @@
   </si>
   <si>
     <t>AstroEnergy</t>
+  </si>
+  <si>
+    <t>Trina</t>
   </si>
 </sst>
 </file>
@@ -790,9 +784,6 @@
     <xf numFmtId="4" fontId="9" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -807,6 +798,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1084,18 +1078,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
     </row>
     <row r="3" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -1129,7 +1123,7 @@
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1141,11 +1135,11 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
@@ -1212,11 +1206,11 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
     </row>
     <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
@@ -1275,11 +1269,11 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="29" t="s">
+      <c r="A29" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
     </row>
     <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
@@ -1397,16 +1391,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -1699,7 +1693,7 @@
         <v>85</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>71</v>
@@ -1725,7 +1719,7 @@
         <v>85</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>71</v>
@@ -1751,7 +1745,7 @@
         <v>85</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>71</v>
@@ -1777,7 +1771,7 @@
         <v>85</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>71</v>
@@ -1803,7 +1797,7 @@
         <v>85</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>71</v>
@@ -1829,7 +1823,7 @@
         <v>85</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>71</v>
@@ -1855,7 +1849,7 @@
         <v>85</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>71</v>
@@ -1881,7 +1875,7 @@
         <v>85</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>71</v>
@@ -1907,7 +1901,7 @@
         <v>85</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>71</v>
@@ -1933,7 +1927,7 @@
         <v>85</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>71</v>
@@ -1959,7 +1953,7 @@
         <v>85</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>71</v>
@@ -2089,7 +2083,7 @@
         <v>85</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>79</v>
@@ -2115,7 +2109,7 @@
         <v>85</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>79</v>
@@ -2141,7 +2135,7 @@
         <v>85</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>79</v>
@@ -2167,7 +2161,7 @@
         <v>85</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>79</v>
@@ -2193,7 +2187,7 @@
         <v>85</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>79</v>
@@ -2219,7 +2213,7 @@
         <v>85</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>79</v>
@@ -2245,7 +2239,7 @@
         <v>85</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>79</v>
@@ -2271,7 +2265,7 @@
         <v>85</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>79</v>
@@ -2297,7 +2291,7 @@
         <v>85</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>79</v>
@@ -2323,7 +2317,7 @@
         <v>85</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>79</v>
@@ -2349,7 +2343,7 @@
         <v>85</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>79</v>
@@ -3011,10 +3005,10 @@
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>72</v>
@@ -3034,7 +3028,7 @@
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>102</v>
@@ -3057,7 +3051,7 @@
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>103</v>
@@ -3080,10 +3074,10 @@
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>72</v>
@@ -3212,7 +3206,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F213540-DFB1-4AE5-8B23-D983343261EE}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="14.140625" customWidth="1"/>
@@ -3237,46 +3231,24 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>107</v>
+        <v>165</v>
       </c>
       <c r="B3">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="C3">
-        <v>285</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>108</v>
+        <v>164</v>
       </c>
       <c r="B4">
-        <v>490</v>
+        <v>460</v>
       </c>
       <c r="C4">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B5">
-        <v>625</v>
-      </c>
-      <c r="C5">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>167</v>
-      </c>
-      <c r="B6">
-        <v>460</v>
-      </c>
-      <c r="C6">
-        <v>285</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -3295,166 +3267,166 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B3">
         <v>5000</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B4">
         <v>8430</v>
       </c>
       <c r="C4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B5">
         <v>15190</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B6">
         <v>500</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B7">
         <v>1600</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B8">
         <v>2500</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B9">
         <v>2000</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B10">
         <v>3500</v>
       </c>
       <c r="C10" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B12">
         <v>200</v>
       </c>
       <c r="C12" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B13">
         <v>170</v>
       </c>
       <c r="C13" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B14">
         <v>230</v>
       </c>
       <c r="C14" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B15">
         <v>450</v>
       </c>
       <c r="C15" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B16">
         <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
